--- a/capstone_guru99/src/test/resources/testdata/CustomerData.xlsx
+++ b/capstone_guru99/src/test/resources/testdata/CustomerData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shahr\eclipse-workspace\wipro-assignment\capstone_guru99\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E97B0CB-2C42-406E-8E0F-78BCBD322530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69A70020-029F-430D-9392-C621B2CA7D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="158">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -491,6 +491,9 @@
   </si>
   <si>
     <t>invalid</t>
+  </si>
+  <si>
+    <t>expectedresult</t>
   </si>
 </sst>
 </file>
@@ -847,15 +850,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="15.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -889,11 +892,14 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M1" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -924,11 +930,11 @@
       <c r="J2" t="s">
         <v>20</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -959,11 +965,11 @@
       <c r="J3" t="s">
         <v>20</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -994,11 +1000,11 @@
       <c r="J4" t="s">
         <v>20</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>34</v>
       </c>
@@ -1029,11 +1035,11 @@
       <c r="J5" t="s">
         <v>20</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -1064,11 +1070,11 @@
       <c r="J6" t="s">
         <v>20</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>50</v>
       </c>
@@ -1099,11 +1105,11 @@
       <c r="J7" t="s">
         <v>20</v>
       </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>57</v>
       </c>
@@ -1134,11 +1140,11 @@
       <c r="J8" t="s">
         <v>20</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>64</v>
       </c>
@@ -1169,11 +1175,11 @@
       <c r="J9" t="s">
         <v>20</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>72</v>
       </c>
@@ -1204,11 +1210,11 @@
       <c r="J10" t="s">
         <v>20</v>
       </c>
-      <c r="L10" t="s">
+      <c r="M10" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>77</v>
       </c>
@@ -1239,11 +1245,11 @@
       <c r="J11" t="s">
         <v>20</v>
       </c>
-      <c r="L11" t="s">
+      <c r="M11" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>85</v>
       </c>
@@ -1271,11 +1277,11 @@
       <c r="J12" t="s">
         <v>20</v>
       </c>
-      <c r="L12" t="s">
+      <c r="M12" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>91</v>
       </c>
@@ -1303,11 +1309,11 @@
       <c r="I13" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L13" t="s">
+      <c r="M13" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>96</v>
       </c>
@@ -1335,11 +1341,11 @@
       <c r="J14" t="s">
         <v>20</v>
       </c>
-      <c r="L14" t="s">
+      <c r="M14" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>103</v>
       </c>
@@ -1367,11 +1373,11 @@
       <c r="J15" t="s">
         <v>20</v>
       </c>
-      <c r="L15" t="s">
+      <c r="M15" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>109</v>
       </c>
@@ -1399,11 +1405,11 @@
       <c r="J16" t="s">
         <v>20</v>
       </c>
-      <c r="L16" t="s">
+      <c r="M16" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>117</v>
       </c>
@@ -1431,11 +1437,11 @@
       <c r="J17" t="s">
         <v>20</v>
       </c>
-      <c r="L17" t="s">
+      <c r="M17" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>124</v>
       </c>
@@ -1463,11 +1469,11 @@
       <c r="J18" t="s">
         <v>20</v>
       </c>
-      <c r="L18" t="s">
+      <c r="M18" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>132</v>
       </c>
@@ -1495,11 +1501,11 @@
       <c r="J19" t="s">
         <v>20</v>
       </c>
-      <c r="L19" t="s">
+      <c r="M19" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>138</v>
       </c>
@@ -1527,11 +1533,11 @@
       <c r="J20" t="s">
         <v>20</v>
       </c>
-      <c r="L20" t="s">
+      <c r="M20" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>145</v>
       </c>
@@ -1559,7 +1565,7 @@
       <c r="J21" t="s">
         <v>20</v>
       </c>
-      <c r="L21" t="s">
+      <c r="M21" t="s">
         <v>156</v>
       </c>
     </row>
